--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/los-lagos.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/los-lagos.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2770.05</v>
+        <v>2778.87</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7242.12</v>
+        <v>7280.63</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2634.54</v>
+        <v>2590.03</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4514.77</v>
+        <v>4450.7</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5504.87</v>
+        <v>5542.87</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3951.81</v>
+        <v>3964.02</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>13551.31</v>
+        <v>13593.2</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>62278.48</v>
+        <v>61448.92</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>22218.85</v>
+        <v>21889.66</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>21932.53</v>
+        <v>21607.58</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>19248.06</v>
+        <v>18962.89</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>55325.29</v>
+        <v>54188.26</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4449.84</v>
+        <v>4467.21</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7681.31</v>
+        <v>7720.45</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3506.14</v>
+        <v>3519.79</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7756.41</v>
+        <v>7717.12</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3205.05</v>
+        <v>3212.4</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>9279.51</v>
+        <v>9344.450000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>11687.12</v>
+        <v>11661.69</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>72323.72</v>
+        <v>71905.10000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/los-lagos.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/los-lagos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Los Lagos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Los Lagos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1002,7 +1002,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1057539-4912-CM26</t>
+          <t>1057539-4865-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>GLOBALMED SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>21889.66</v>
+        <v>18962.89</v>
       </c>
     </row>
     <row r="11">
@@ -1124,7 +1124,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1057539-4865-CM26</t>
+          <t>1057539-4912-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>18962.89</v>
+        <v>21889.66</v>
       </c>
     </row>
     <row r="13">
@@ -1729,6 +1729,433 @@
       </c>
       <c r="M21" s="2" t="n">
         <v>71905.10000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1057539-6078-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>2782.86</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1057539-6141-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>34121.68</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1063538-5841-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>61.602.260-1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>HOSPITAL BASE OSORNO</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>SPINEX CORPORATION CHILE S.A</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>76.166.489-1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>3948.44</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1514-3289-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>61.602.275-k</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>78.566.250-4</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>2479.17</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1057534-1072-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>61.607.602-7</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>2346.8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2048-2421-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61.975.800-5</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1057539-6878-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>GLOBALMED SpA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.400.383-7</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>60585.44</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/los-lagos.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Spinex Corporation Chile S.A</t>
+          <t>SPINEX CORPORATION CHILE S.A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Spinex Corporation Chile S.A</t>
+          <t>SPINEX CORPORATION CHILE S.A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2156,6 +2156,1348 @@
       </c>
       <c r="M28" s="2" t="n">
         <v>60585.44</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1063538-6400-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>61.602.260-1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>HOSPITAL BASE OSORNO</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>2567.28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1057539-7181-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>BIOIMPLANTES SA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>76.214.144-2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>12315.46</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1057539-7216-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>76374.17999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1057539-7288-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>7601.14</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1057539-7289-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>74730.62</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1057539-7405-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>72780.28</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1057539-7408-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>5088.08</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1057539-7619-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>BIOIMPLANTES SA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.214.144-2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>72993.36</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1057539-7603-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>5041.03</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1057539-7572-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>BIOIMPLANTES SA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.214.144-2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>7299.34</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1057539-7407-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>55324.51</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1057539-7406-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>67456.19</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1057539-7692-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>OSTEOTRAUMA SPA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>76.965.562-K</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>16694.48</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1057539-7898-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>28598.42</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1057539-7998-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>7430.79</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1057539-8024-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>SINERMED SPA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>76.367.671-4</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>28095.39</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1057539-7411-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>64519.04</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1057539-8032-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>12096.26</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1057539-8040-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>12096.26</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1057539-8097-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>2341.47</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2048-2857-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>61.975.800-5</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>2256.49</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1057539-8154-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>SINERMED SPA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>76.367.671-4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>5518</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/los-lagos.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/los-lagos.xlsx
@@ -562,7 +562,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +810,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1123,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1554,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1741,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1867,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2115,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2424,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2611,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2737,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3107,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3416,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3481,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/los-lagos.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -827,7 +827,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1057539-4560-CM26</t>
+          <t>1057539-4657-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -867,28 +867,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3964.02</v>
+        <v>13593.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1057539-4657-CM26</t>
+          <t>1057539-4560-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -908,7 +912,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -928,26 +932,22 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.671-4</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>13593.2</v>
+        <v>3964.02</v>
       </c>
     </row>
     <row r="9">
@@ -1014,7 +1014,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1057539-4865-CM26</t>
+          <t>1057539-4912-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>18962.89</v>
+        <v>21889.66</v>
       </c>
     </row>
     <row r="11">
@@ -1140,7 +1140,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1057539-4912-CM26</t>
+          <t>1057539-4865-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>21889.66</v>
+        <v>18962.89</v>
       </c>
     </row>
     <row r="13">
@@ -1249,7 +1249,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2193,7 +2197,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1063538-6400-CM26</t>
+          <t>1057539-7216-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2213,17 +2217,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.602.260-1</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HOSPITAL BASE OSORNO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2233,12 +2237,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2248,13 +2252,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2567.28</v>
+        <v>76374.17999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1057539-7181-CM26</t>
+          <t>1063538-6400-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2274,17 +2278,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.602.260-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2294,28 +2298,32 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>12315.46</v>
+        <v>2567.28</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1057539-7216-CM26</t>
+          <t>1057539-7181-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2355,12 +2363,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.214.144-2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2370,13 +2378,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>76374.17999999999</v>
+        <v>12315.46</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1057539-7288-CM26</t>
+          <t>1057539-7289-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2416,32 +2424,28 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7601.14</v>
+        <v>74730.62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1057539-7289-CM26</t>
+          <t>1057539-7287-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2481,12 +2485,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2496,13 +2500,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>74730.62</v>
+        <v>54179.57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1057539-7405-CM26</t>
+          <t>1057539-7288-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2517,7 +2521,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2542,28 +2546,32 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>72780.28</v>
+        <v>7601.14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1057539-7408-CM26</t>
+          <t>1057539-7290-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2578,7 +2586,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2603,32 +2611,28 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.585.860-6</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>5088.08</v>
+        <v>66609</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1057539-7619-CM26</t>
+          <t>1057539-7408-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2643,7 +2647,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2668,28 +2672,32 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>72993.36</v>
+        <v>5088.08</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1057539-7603-CM26</t>
+          <t>1057539-7405-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2704,7 +2712,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2729,32 +2737,28 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>5041.03</v>
+        <v>72780.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1057539-7572-CM26</t>
+          <t>1057539-7407-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2794,12 +2798,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2809,13 +2813,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>7299.34</v>
+        <v>55324.51</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1057539-7407-CM26</t>
+          <t>1057539-7572-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2835,7 +2839,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2855,12 +2859,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.214.144-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2870,13 +2874,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>55324.51</v>
+        <v>7299.34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1057539-7406-CM26</t>
+          <t>1057539-7603-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2896,7 +2900,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2916,28 +2920,32 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>67456.19</v>
+        <v>5041.03</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1057539-7692-CM26</t>
+          <t>1057539-7619-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2952,12 +2960,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2977,12 +2985,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>OSTEOTRAUMA SPA</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.965.562-K</t>
+          <t>76.214.144-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2992,13 +3000,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>16694.48</v>
+        <v>72993.36</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1057539-7898-CM26</t>
+          <t>1057539-7406-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3013,7 +3021,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3053,13 +3061,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>28598.42</v>
+        <v>67456.19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1057539-7998-CM26</t>
+          <t>1057539-7692-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3074,7 +3082,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3099,32 +3107,28 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>OSTEOTRAUMA SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.965.562-K</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7430.79</v>
+        <v>16694.48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1057539-8024-CM26</t>
+          <t>1057539-7898-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3139,7 +3143,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3164,12 +3168,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3179,13 +3183,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>28095.39</v>
+        <v>28598.42</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1057539-7411-CM26</t>
+          <t>1057539-7998-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3200,7 +3204,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3225,28 +3229,32 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>64519.04</v>
+        <v>7430.79</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057539-8032-CM26</t>
+          <t>1057539-8024-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3261,7 +3269,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3286,12 +3294,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3301,7 +3309,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>12096.26</v>
+        <v>28095.39</v>
       </c>
     </row>
     <row r="47">
@@ -3368,7 +3376,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1057539-8097-CM26</t>
+          <t>1057539-8032-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3383,7 +3391,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3408,32 +3416,28 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2341.47</v>
+        <v>12096.26</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2048-2857-CM26</t>
+          <t>1057539-7513-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3448,7 +3452,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3458,12 +3462,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.975.800-5</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3473,32 +3477,28 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.585.860-6</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2256.49</v>
+        <v>70972.92999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1057539-8154-CM26</t>
+          <t>1057539-7411-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3553,7 +3553,751 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
+        <v>64519.04</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1057539-8097-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>2341.47</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1057539-7515-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>TECNOMEDICAL S A</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>99.585.860-6</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>15634.34</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1057539-8154-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>SINERMED SPA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>76.367.671-4</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
         <v>5518</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2048-2857-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>61.975.800-5</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>2256.49</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1057539-8240-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>SPINEX CORPORATION CHILE S.A</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>76.166.489-1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>43904.23</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1057539-8225-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>9400.209999999999</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1514-3986-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>61.602.275-k</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>SPINEX CORPORATION CHILE S.A</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>76.166.489-1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>8995.41</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1057539-8284-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>AETICA SPA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>63086.71</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1057539-8281-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>BIOIMPLANTES SA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>76.214.144-2</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>57072.05</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1057539-8551-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>3751.95</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1057539-8853-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Sylex Biomédica Spa</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76.015.781-3</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>3817.75</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1057539-8282-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>BIOIMPLANTES SA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>76.214.144-2</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>57980.76</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/los-lagos.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057534-1072-CM26</t>
+          <t>1057539-6536-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2025,22 +2025,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2065,13 +2065,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2346.8</v>
+        <v>3583.75</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2048-2421-CM26</t>
+          <t>1057534-1072-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2086,22 +2086,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.975.800-5</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2111,32 +2111,28 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2385</v>
+        <v>2346.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1057539-6878-CM26</t>
+          <t>2048-2421-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2151,22 +2147,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.975.800-5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2176,28 +2172,32 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>60585.44</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1057539-7216-CM26</t>
+          <t>1057539-6878-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2252,13 +2252,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>76374.17999999999</v>
+        <v>60585.44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1063538-6400-CM26</t>
+          <t>1057539-7216-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2278,17 +2278,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.602.260-1</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HOSPITAL BASE OSORNO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2298,32 +2298,28 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2567.28</v>
+        <v>76374.17999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1057539-7181-CM26</t>
+          <t>1063538-6400-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2343,17 +2339,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.602.260-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2363,28 +2359,32 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>12315.46</v>
+        <v>2567.28</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1057539-7289-CM26</t>
+          <t>1057539-7181-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2424,12 +2424,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.214.144-2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>74730.62</v>
+        <v>12315.46</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1057539-7287-CM26</t>
+          <t>1057539-7289-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2500,13 +2500,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>54179.57</v>
+        <v>74730.62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1057539-7288-CM26</t>
+          <t>1057539-7287-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2546,32 +2546,28 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.585.860-6</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>7601.14</v>
+        <v>54179.57</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1057539-7290-CM26</t>
+          <t>1057539-7288-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2611,28 +2607,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>66609</v>
+        <v>7601.14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1057539-7408-CM26</t>
+          <t>1057539-7290-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2672,26 +2672,22 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.585.860-6</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>5088.08</v>
+        <v>66609</v>
       </c>
     </row>
     <row r="37">
@@ -2758,7 +2754,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1057539-7407-CM26</t>
+          <t>1057539-7408-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2773,7 +2769,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2798,28 +2794,32 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>55324.51</v>
+        <v>5088.08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1057539-7572-CM26</t>
+          <t>1057539-7406-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2874,13 +2874,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7299.34</v>
+        <v>67456.19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1057539-7603-CM26</t>
+          <t>1057539-7407-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2920,32 +2920,28 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>5041.03</v>
+        <v>55324.51</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1057539-7619-CM26</t>
+          <t>1057539-7572-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3000,13 +2996,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>72993.36</v>
+        <v>7299.34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1057539-7406-CM26</t>
+          <t>1057539-7603-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3026,7 +3022,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3046,28 +3042,32 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>67456.19</v>
+        <v>5041.03</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1057539-7692-CM26</t>
+          <t>1057539-7619-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>OSTEOTRAUMA SPA</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.965.562-K</t>
+          <t>76.214.144-2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3122,13 +3122,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>16694.48</v>
+        <v>72993.36</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1057539-7898-CM26</t>
+          <t>1057539-7692-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>OSTEOTRAUMA SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.965.562-K</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3183,13 +3183,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>28598.42</v>
+        <v>16694.48</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1057539-7998-CM26</t>
+          <t>1057539-7898-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3229,32 +3229,28 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>7430.79</v>
+        <v>28598.42</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057539-8024-CM26</t>
+          <t>1057539-7998-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3269,7 +3265,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3294,28 +3290,32 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>28095.39</v>
+        <v>7430.79</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1057539-8040-CM26</t>
+          <t>1057539-8024-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3370,13 +3370,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>12096.26</v>
+        <v>28095.39</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1057539-8032-CM26</t>
+          <t>1057539-8040-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3437,7 +3437,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1057539-7513-CM26</t>
+          <t>1057539-8032-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3492,13 +3492,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>70972.92999999999</v>
+        <v>12096.26</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1057539-7411-CM26</t>
+          <t>1057539-7513-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3553,13 +3553,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>64519.04</v>
+        <v>70972.92999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1057539-8097-CM26</t>
+          <t>1057539-7411-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3599,32 +3599,28 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2341.47</v>
+        <v>64519.04</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1057539-7515-CM26</t>
+          <t>1057539-8097-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3639,12 +3635,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3664,28 +3660,32 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>15634.34</v>
+        <v>2341.47</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1057539-8154-CM26</t>
+          <t>1057539-7515-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5518</v>
+        <v>15634.34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2048-2857-CM26</t>
+          <t>1057539-8154-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.975.800-5</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3786,32 +3786,28 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.671-4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2256.49</v>
+        <v>5518</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1057539-8240-CM26</t>
+          <t>2048-2857-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3821,12 +3817,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3836,12 +3832,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.975.800-5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3851,28 +3847,32 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SPINEX CORPORATION CHILE S.A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.166.489-1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>43904.23</v>
+        <v>2256.49</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1057539-8225-CM26</t>
+          <t>1057539-8240-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>SPINEX CORPORATION CHILE S.A</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.166.489-1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3927,13 +3927,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>9400.209999999999</v>
+        <v>43904.23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1514-3986-CM26</t>
+          <t>1057539-8225-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SPINEX CORPORATION CHILE S.A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.166.489-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3988,13 +3988,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>8995.41</v>
+        <v>9400.209999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1057539-8284-CM26</t>
+          <t>1514-3986-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4019,12 +4019,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4034,32 +4034,28 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>SPINEX CORPORATION CHILE S.A</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.166.489-1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>63086.71</v>
+        <v>8995.41</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1057539-8281-CM26</t>
+          <t>1057539-8284-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4099,28 +4095,32 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>57072.05</v>
+        <v>63086.71</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1057539-8551-CM26</t>
+          <t>1057539-8281-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.214.144-2</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4175,13 +4175,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3751.95</v>
+        <v>57072.05</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1057539-8853-CM26</t>
+          <t>1057539-8551-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Sylex Biomédica Spa</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.015.781-3</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4236,13 +4236,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3817.75</v>
+        <v>3751.95</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057539-8282-CM26</t>
+          <t>1057539-8853-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>Sylex Biomédica Spa</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
+          <t>76.015.781-3</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4297,6 +4297,67 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
+        <v>3817.75</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1057539-8282-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>BIOIMPLANTES SA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>76.214.144-2</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
         <v>57980.76</v>
       </c>
     </row>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/los-lagos.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/los-lagos.xlsx
@@ -4014,7 +4014,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
